--- a/data/trans_orig/P20D1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por un hombre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,51%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>442</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>53,49%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>760</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>19558</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,33%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>358</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>313</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -3123,97 +3123,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3752</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3433</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>34,57%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3655</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45022</t>
+          <t>46223</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64619</t>
+          <t>65634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29774</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>25395</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45464</t>
+          <t>44523</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P20D1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>934</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>500</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>417</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18159</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>513</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11482</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15412</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19558</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>355</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>406</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>36025</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46933</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>55556</t>
+          <t>64970</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>53543</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65634</t>
+          <t>74906</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>20103</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12845</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29205</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25859</t>
+          <t>29028</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20499</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>34504</t>
+          <t>37757</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44523</t>
+          <t>49496</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
